--- a/fhir/StructureDefinition-ehealth-communication.xlsx
+++ b/fhir/StructureDefinition-ehealth-communication.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -352,7 +352,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -636,7 +636,7 @@
     <t>Communication.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|ActivityDefinition|Measure|OperationDefinition|Questionnaire)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1|Questionnaire|4.0.1)
 </t>
   </si>
   <si>
@@ -709,7 +709,7 @@
     <t>Communication.inResponseTo</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Communication)
+    <t xml:space="preserve">Reference(Communication|4.0.1)
 </t>
   </si>
   <si>
@@ -772,7 +772,7 @@
     <t>Codes for the reason why a communication did not happen.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/communication-not-done-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/communication-not-done-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -873,7 +873,7 @@
     <t>Codes describing the purpose or content of the communication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/communication-topic</t>
+    <t>http://hl7.org/fhir/ValueSet/communication-topic|4.0.1</t>
   </si>
   <si>
     <t>FiveWs.context</t>
@@ -882,7 +882,7 @@
     <t>Communication.about</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -898,7 +898,7 @@
     <t>Communication.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -988,7 +988,7 @@
     <t>Codes for describing reasons for the occurrence of a communication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1422,7 +1422,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="61.75" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.1953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.72265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/fhir/StructureDefinition-ehealth-communication.xlsx
+++ b/fhir/StructureDefinition-ehealth-communication.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-communication.xlsx
+++ b/fhir/StructureDefinition-ehealth-communication.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-communication.xlsx
+++ b/fhir/StructureDefinition-ehealth-communication.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-communication.xlsx
+++ b/fhir/StructureDefinition-ehealth-communication.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-communication.xlsx
+++ b/fhir/StructureDefinition-ehealth-communication.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-communication.xlsx
+++ b/fhir/StructureDefinition-ehealth-communication.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
